--- a/테이블/몬스터/몬스터 데이터 테이블.xlsx
+++ b/테이블/몬스터/몬스터 데이터 테이블.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addmin\Desktop\Unreal\Project TirgerGhostField\기획\테이블\몬스터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD7E349-5E37-4079-B131-2EEA18200ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4178406F-318F-45A3-9A5E-B71CFF764F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="도메인 정의" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>속성 명칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -831,7 +831,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C19B3A-9DE6-4959-8646-89E4535BEFF0}">
-  <dimension ref="B1:I1"/>
+  <dimension ref="B1:I4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
@@ -876,6 +876,84 @@
         <v>개체 발악 조건</v>
       </c>
     </row>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>1000</v>
+      </c>
+      <c r="C2">
+        <v>150</v>
+      </c>
+      <c r="D2">
+        <v>200</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>1001</v>
+      </c>
+      <c r="C3">
+        <v>150</v>
+      </c>
+      <c r="D3">
+        <v>200</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>1002</v>
+      </c>
+      <c r="C4">
+        <v>150</v>
+      </c>
+      <c r="D4">
+        <v>200</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
